--- a/public/templates/template_import_ustadz.xlsx
+++ b/public/templates/template_import_ustadz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tamam\Herd\sia\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAB29C2-F039-4486-AE83-828439608B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED3DBF9-8865-4477-A177-57DAAA5F9AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E4F09937-6EAF-4319-B60C-264F9E558CD0}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Nama</t>
   </si>
   <si>
     <t>No Telp</t>
-  </si>
-  <si>
-    <t>Email</t>
   </si>
   <si>
     <t>&gt;&gt; Ini Baris Contoh, Hapus baris ini jika hendak import</t>
@@ -46,7 +43,7 @@
     <t>Ust. Fulan</t>
   </si>
   <si>
-    <t>ustfulan@gmail.com</t>
+    <t>NIS</t>
   </si>
 </sst>
 </file>
@@ -934,32 +931,32 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+      <c r="C2" s="2">
+        <v>10001</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{AD78DC7A-BA0C-4C7E-948D-1C8C7D7A5F03}"/>
+    <hyperlink ref="C2" r:id="rId1" display="ustfulan@gmail.com" xr:uid="{AD78DC7A-BA0C-4C7E-948D-1C8C7D7A5F03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
